--- a/laptop_register.xlsx
+++ b/laptop_register.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laptops" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resignation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resignation'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,110 +438,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Employee (Arabic)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Employee (English)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Employee code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Computer name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Serial number</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>RAM</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Assigned on</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Assigned by</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Ended on</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -548,80 +556,606 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>احمد محمد احمد</t>
+          <t>عمر اشرف احمد حبيب</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Omar Ashraf Ahmed Habib</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ohabib@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SLOHabibR</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PF5LX0S6</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>مروة طارق احمد صبحي</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Marwa Tarek Ahmed Sobhy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>1351</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ymohamed@stm.com.eg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>matarek@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SLMAtarekR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PF5P93DS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Majad</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>فيصل هاني امام</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Faisal hany Emam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>femam@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SLFEmamR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PF5NG1YN</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>خالد عبد الخالق عبد المحسن</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Khaled Abdelkhalek Abdelmohsen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>kelsabahy@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FMKElsabahyR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PF5W5TXH</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>احمد ابراهيم صدقي</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ahmed Ibrahim Sedky</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>asedky@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ADASedkyR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PK5PJ7T</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>I5</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PF5MDKBP</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>24GB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>512SSD</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>BLACK</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Laptop handover</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>15-Sep-26</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Mohamed Taha</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Held</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>محمد شعبان ابراهيم</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mshaban@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SLMShabanR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PF5MG6KD</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q2"/>
+  <autoFilter ref="A1:R7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee (Arabic)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Employee (English)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Employee code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Left on</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Recorded by</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Held at the time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Naity Mahmoud</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>nmahmoud@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/laptop_register.xlsx
+++ b/laptop_register.xlsx
@@ -979,7 +979,11 @@
           <t>محمد شعبان ابراهيم</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mohamed Shaban Ibrahim</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>1356</t>
@@ -1123,11 +1127,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>نايتي محمود</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Naity Mahmoud</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Administration</t>

--- a/laptop_register.xlsx
+++ b/laptop_register.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resignation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resignation'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -556,17 +556,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>عمر اشرف احمد حبيب</t>
+          <t>نهي عبدالرازق احمد</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Omar Ashraf Ahmed Habib</t>
+          <t>Noha Abdelrazek Ahmed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ohabib@stm.com.eg</t>
+          <t>nabdelrazek@stm.com.eg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SLOHabibR</t>
+          <t>SLNAbdelrazekR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PF5LX0S6</t>
+          <t>PF5T92HE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>16-Sep-26</t>
+          <t>17-Sep-26</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -640,17 +640,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>مروة طارق احمد صبحي</t>
+          <t>عمر اشرف احمد حبيب</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marwa Tarek Ahmed Sobhy</t>
+          <t>Omar Ashraf Ahmed Habib</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>matarek@stm.com.eg</t>
+          <t>ohabib@stm.com.eg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SLMAtarekR</t>
+          <t>SLOHabibR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PF5P93DS</t>
+          <t>PF5LX0S6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Majad</t>
+          <t>Mohamed Taha</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>فيصل هاني امام</t>
+          <t>مروة طارق احمد صبحي</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Faisal hany Emam</t>
+          <t>Marwa Tarek Ahmed Sobhy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>femam@stm.com.eg</t>
+          <t>matarek@stm.com.eg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SLFEmamR</t>
+          <t>SLMAtarekR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PF5NG1YN</t>
+          <t>PF5P93DS</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>I5</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mohamed Taha</t>
+          <t>Majad</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -808,32 +808,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>خالد عبد الخالق عبد المحسن</t>
+          <t>فيصل هاني امام</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Khaled Abdelkhalek Abdelmohsen</t>
+          <t>Faisal hany Emam</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FM</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>kelsabahy@stm.com.eg</t>
+          <t>femam@stm.com.eg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FMKElsabahyR</t>
+          <t>SLFEmamR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PF5W5TXH</t>
+          <t>PF5NG1YN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>I5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -892,42 +892,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>احمد ابراهيم صدقي</t>
+          <t>خالد عبد الخالق عبد المحسن</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim Sedky</t>
+          <t>Khaled Abdelkhalek Abdelmohsen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>FM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>asedky@stm.com.eg</t>
+          <t>kelsabahy@stm.com.eg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ADASedkyR</t>
+          <t>FMKElsabahyR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PF5MDKBP</t>
+          <t>PF5W5TXH</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,32 +976,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>محمد شعبان ابراهيم</t>
+          <t>احمد ابراهيم صدقي</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mohamed Shaban Ibrahim</t>
+          <t>Ahmed Ibrahim Sedky</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mshaban@stm.com.eg</t>
+          <t>asedky@stm.com.eg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SLMShabanR</t>
+          <t>ADASedkyR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PF5MG6KD</t>
+          <t>PF5MDKBP</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1057,8 +1057,92 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>محمد شعبان ابراهيم</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mohamed Shaban Ibrahim</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mshaban@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SLMShabanR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PF5MG6KD</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R7"/>
+  <autoFilter ref="A1:R8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/laptop_register.xlsx
+++ b/laptop_register.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resignation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resignation'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -556,32 +556,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>نهي عبدالرازق احمد</t>
+          <t>مهند حماده جنش</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Noha Abdelrazek Ahmed</t>
+          <t>Mohannad Hamada Ganash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>nabdelrazek@stm.com.eg</t>
+          <t>mhamada@stm.com.eg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SLNAbdelrazekR</t>
+          <t>ITMHamadaR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PF5T92HE</t>
+          <t>PF5NBNBH</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -640,17 +640,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>عمر اشرف احمد حبيب</t>
+          <t>سارة نبيل جورجي جرجس</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Omar Ashraf Ahmed Habib</t>
+          <t>Sara Nabil Gorgy Girgis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ohabib@stm.com.eg</t>
+          <t>sanabil@stm.com.eg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SLOHabibR</t>
+          <t>SLSAnabilR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -675,12 +675,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PF5LX0S6</t>
+          <t>PF5NDMEY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>16-Sep-26</t>
+          <t>17-Sep-26</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mohamed Taha</t>
+          <t>Majad</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>مروة طارق احمد صبحي</t>
+          <t>نهي عبدالرازق احمد</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marwa Tarek Ahmed Sobhy</t>
+          <t>Noha Abdelrazek Ahmed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>matarek@stm.com.eg</t>
+          <t>nabdelrazek@stm.com.eg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SLMAtarekR</t>
+          <t>SLNAbdelrazekR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PF5P93DS</t>
+          <t>PF5T92HE</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>16-Sep-26</t>
+          <t>17-Sep-26</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Majad</t>
+          <t>Mohamed Taha</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -808,17 +808,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>فيصل هاني امام</t>
+          <t>عمر اشرف احمد حبيب</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Faisal hany Emam</t>
+          <t>Omar Ashraf Ahmed Habib</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>femam@stm.com.eg</t>
+          <t>ohabib@stm.com.eg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SLFEmamR</t>
+          <t>SLOHabibR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PF5NG1YN</t>
+          <t>PF5LX0S6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>I5</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -892,32 +892,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>خالد عبد الخالق عبد المحسن</t>
+          <t>مروة طارق احمد صبحي</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Khaled Abdelkhalek Abdelmohsen</t>
+          <t>Marwa Tarek Ahmed Sobhy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FM</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>kelsabahy@stm.com.eg</t>
+          <t>matarek@stm.com.eg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FMKElsabahyR</t>
+          <t>SLMAtarekR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PF5W5TXH</t>
+          <t>PF5P93DS</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Mohamed Taha</t>
+          <t>Majad</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -976,47 +976,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>احمد ابراهيم صدقي</t>
+          <t>فيصل هاني امام</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim Sedky</t>
+          <t>Faisal hany Emam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>asedky@stm.com.eg</t>
+          <t>femam@stm.com.eg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ADASedkyR</t>
+          <t>SLFEmamR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PF5MDKBP</t>
+          <t>PF5NG1YN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>I5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1060,47 +1060,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>محمد شعبان ابراهيم</t>
+          <t>خالد عبد الخالق عبد المحسن</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mohamed Shaban Ibrahim</t>
+          <t>Khaled Abdelkhalek Abdelmohsen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>FM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mshaban@stm.com.eg</t>
+          <t>kelsabahy@stm.com.eg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SLMShabanR</t>
+          <t>FMKElsabahyR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PF5MG6KD</t>
+          <t>PF5W5TXH</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1141,8 +1141,176 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>احمد ابراهيم صدقي</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ahmed Ibrahim Sedky</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>asedky@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ADASedkyR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PF5MDKBP</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>محمد شعبان ابراهيم</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mohamed Shaban Ibrahim</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mshaban@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SLMShabanR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PF5MG6KD</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16-Sep-26</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Mohamed Taha</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R8"/>
+  <autoFilter ref="A1:R10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/laptop_register.xlsx
+++ b/laptop_register.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PF5P93DS</t>
+          <t>PF63RCYV</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/laptop_register.xlsx
+++ b/laptop_register.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resignation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Laptops'!$A$1:$R$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resignation'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -640,17 +640,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>سارة نبيل جورجي جرجس</t>
+          <t>نهي عبدالرازق احمد</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sara Nabil Gorgy Girgis</t>
+          <t>Noha Abdelrazek Ahmed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sanabil@stm.com.eg</t>
+          <t>nabdelrazek@stm.com.eg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SLSAnabilR</t>
+          <t>SLNAbdelrazekR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PF5NDMEY</t>
+          <t>PF5T92HE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Majad</t>
+          <t>Mohamed Taha</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>نهي عبدالرازق احمد</t>
+          <t>سارة نبيل جورجي جرجس</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Noha Abdelrazek Ahmed</t>
+          <t>Sara Nabil Gorgy Girgis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>nabdelrazek@stm.com.eg</t>
+          <t>sanabil@stm.com.eg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SLNAbdelrazekR</t>
+          <t>SLSAnabilR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PF5T92HE</t>
+          <t>PF5NDMEY</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mohamed Taha</t>
+          <t>Majad</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>مروة طارق احمد صبحي</t>
+          <t>فيصل هاني امام</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marwa Tarek Ahmed Sobhy</t>
+          <t>Faisal hany Emam</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>matarek@stm.com.eg</t>
+          <t>femam@stm.com.eg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SLMAtarekR</t>
+          <t>SLFEmamR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PF63RCYV</t>
+          <t>PF5NG1YN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>I5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Majad</t>
+          <t>Mohamed Taha</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -976,47 +976,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>فيصل هاني امام</t>
+          <t>احمد ابراهيم صدقي</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Faisal hany Emam</t>
+          <t>Ahmed Ibrahim Sedky</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>femam@stm.com.eg</t>
+          <t>asedky@stm.com.eg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SLFEmamR</t>
+          <t>ADASedkyR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PF5NG1YN</t>
+          <t>PF5MDKBP</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>I5</t>
+          <t>I7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1144,47 +1144,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>احمد ابراهيم صدقي</t>
+          <t>مروة طارق احمد صبحي</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ahmed Ibrahim Sedky</t>
+          <t>Marwa Tarek Ahmed Sobhy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>asedky@stm.com.eg</t>
+          <t>matarek@stm.com.eg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ADASedkyR</t>
+          <t>SLMAtarekR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PF5MDKBP</t>
+          <t>PF63RCYV</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>I7</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Mohamed Taha</t>
+          <t>Majad</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1309,8 +1309,92 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>نوران هشام البحيري</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Noran Hesham El Behairy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>nelbeheiry@stm.com.eg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SLNElbeheiryR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PF5KQJJV</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24GB</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>512SSD</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Laptop handover</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>13-Sep-26</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>JINX</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R10"/>
+  <autoFilter ref="A1:R11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
